--- a/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4108EB9D-31D7-4A5C-B723-EEE2882B053E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A1046E-0C72-4D29-B1CD-875DDEB77030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5353,7 +5353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D70302-BCFD-4B96-B021-2492B6682FDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39767280-4410-4AC4-A28C-CE5631CEF6C5}">
   <dimension ref="B3:H64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A1046E-0C72-4D29-B1CD-875DDEB77030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D785A7-3AB7-4A7D-857E-D514F4E4F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5353,7 +5353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39767280-4410-4AC4-A28C-CE5631CEF6C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BBB0A9-71EA-4B64-A610-1E86851A7E05}">
   <dimension ref="B3:H64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D785A7-3AB7-4A7D-857E-D514F4E4F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CD7383-6A28-4B60-B33F-B72DF418A2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1175,184 +1175,184 @@
     <t>grid node -- sol9</t>
   </si>
   <si>
-    <t>e_wof41</t>
-  </si>
-  <si>
-    <t>grid node -- wof41</t>
-  </si>
-  <si>
-    <t>e_wof42</t>
-  </si>
-  <si>
-    <t>grid node -- wof42</t>
-  </si>
-  <si>
-    <t>e_wof43</t>
-  </si>
-  <si>
-    <t>grid node -- wof43</t>
-  </si>
-  <si>
-    <t>e_wof44</t>
-  </si>
-  <si>
-    <t>grid node -- wof44</t>
-  </si>
-  <si>
-    <t>e_wof45</t>
-  </si>
-  <si>
-    <t>grid node -- wof45</t>
-  </si>
-  <si>
-    <t>e_wof46</t>
-  </si>
-  <si>
-    <t>grid node -- wof46</t>
-  </si>
-  <si>
-    <t>e_wof47</t>
-  </si>
-  <si>
-    <t>grid node -- wof47</t>
-  </si>
-  <si>
-    <t>e_wof48</t>
-  </si>
-  <si>
-    <t>grid node -- wof48</t>
-  </si>
-  <si>
-    <t>e_wof49</t>
-  </si>
-  <si>
-    <t>grid node -- wof49</t>
-  </si>
-  <si>
-    <t>e_wof50</t>
-  </si>
-  <si>
-    <t>grid node -- wof50</t>
-  </si>
-  <si>
-    <t>e_won21</t>
-  </si>
-  <si>
-    <t>grid node -- won21</t>
-  </si>
-  <si>
-    <t>e_won22</t>
-  </si>
-  <si>
-    <t>grid node -- won22</t>
-  </si>
-  <si>
-    <t>e_won23</t>
-  </si>
-  <si>
-    <t>grid node -- won23</t>
-  </si>
-  <si>
-    <t>e_won24</t>
-  </si>
-  <si>
-    <t>grid node -- won24</t>
-  </si>
-  <si>
-    <t>e_won25</t>
-  </si>
-  <si>
-    <t>grid node -- won25</t>
-  </si>
-  <si>
-    <t>e_won26</t>
-  </si>
-  <si>
-    <t>grid node -- won26</t>
-  </si>
-  <si>
-    <t>e_won27</t>
-  </si>
-  <si>
-    <t>grid node -- won27</t>
-  </si>
-  <si>
-    <t>e_won28</t>
-  </si>
-  <si>
-    <t>grid node -- won28</t>
-  </si>
-  <si>
-    <t>e_won29</t>
-  </si>
-  <si>
-    <t>grid node -- won29</t>
-  </si>
-  <si>
-    <t>e_won30</t>
-  </si>
-  <si>
-    <t>grid node -- won30</t>
-  </si>
-  <si>
-    <t>e_won31</t>
-  </si>
-  <si>
-    <t>grid node -- won31</t>
-  </si>
-  <si>
-    <t>e_won32</t>
-  </si>
-  <si>
-    <t>grid node -- won32</t>
-  </si>
-  <si>
-    <t>e_won33</t>
-  </si>
-  <si>
-    <t>grid node -- won33</t>
-  </si>
-  <si>
-    <t>e_won34</t>
-  </si>
-  <si>
-    <t>grid node -- won34</t>
-  </si>
-  <si>
-    <t>e_won35</t>
-  </si>
-  <si>
-    <t>grid node -- won35</t>
-  </si>
-  <si>
-    <t>e_won36</t>
-  </si>
-  <si>
-    <t>grid node -- won36</t>
-  </si>
-  <si>
-    <t>e_won37</t>
-  </si>
-  <si>
-    <t>grid node -- won37</t>
-  </si>
-  <si>
-    <t>e_won38</t>
-  </si>
-  <si>
-    <t>grid node -- won38</t>
-  </si>
-  <si>
-    <t>e_won39</t>
-  </si>
-  <si>
-    <t>grid node -- won39</t>
-  </si>
-  <si>
-    <t>e_won40</t>
-  </si>
-  <si>
-    <t>grid node -- won40</t>
+    <t>e_wof1</t>
+  </si>
+  <si>
+    <t>grid node -- wof1</t>
+  </si>
+  <si>
+    <t>e_wof10</t>
+  </si>
+  <si>
+    <t>grid node -- wof10</t>
+  </si>
+  <si>
+    <t>e_wof2</t>
+  </si>
+  <si>
+    <t>grid node -- wof2</t>
+  </si>
+  <si>
+    <t>e_wof3</t>
+  </si>
+  <si>
+    <t>grid node -- wof3</t>
+  </si>
+  <si>
+    <t>e_wof4</t>
+  </si>
+  <si>
+    <t>grid node -- wof4</t>
+  </si>
+  <si>
+    <t>e_wof5</t>
+  </si>
+  <si>
+    <t>grid node -- wof5</t>
+  </si>
+  <si>
+    <t>e_wof6</t>
+  </si>
+  <si>
+    <t>grid node -- wof6</t>
+  </si>
+  <si>
+    <t>e_wof7</t>
+  </si>
+  <si>
+    <t>grid node -- wof7</t>
+  </si>
+  <si>
+    <t>e_wof8</t>
+  </si>
+  <si>
+    <t>grid node -- wof8</t>
+  </si>
+  <si>
+    <t>e_wof9</t>
+  </si>
+  <si>
+    <t>grid node -- wof9</t>
+  </si>
+  <si>
+    <t>e_won1</t>
+  </si>
+  <si>
+    <t>grid node -- won1</t>
+  </si>
+  <si>
+    <t>e_won10</t>
+  </si>
+  <si>
+    <t>grid node -- won10</t>
+  </si>
+  <si>
+    <t>e_won11</t>
+  </si>
+  <si>
+    <t>grid node -- won11</t>
+  </si>
+  <si>
+    <t>e_won12</t>
+  </si>
+  <si>
+    <t>grid node -- won12</t>
+  </si>
+  <si>
+    <t>e_won13</t>
+  </si>
+  <si>
+    <t>grid node -- won13</t>
+  </si>
+  <si>
+    <t>e_won14</t>
+  </si>
+  <si>
+    <t>grid node -- won14</t>
+  </si>
+  <si>
+    <t>e_won15</t>
+  </si>
+  <si>
+    <t>grid node -- won15</t>
+  </si>
+  <si>
+    <t>e_won16</t>
+  </si>
+  <si>
+    <t>grid node -- won16</t>
+  </si>
+  <si>
+    <t>e_won17</t>
+  </si>
+  <si>
+    <t>grid node -- won17</t>
+  </si>
+  <si>
+    <t>e_won18</t>
+  </si>
+  <si>
+    <t>grid node -- won18</t>
+  </si>
+  <si>
+    <t>e_won19</t>
+  </si>
+  <si>
+    <t>grid node -- won19</t>
+  </si>
+  <si>
+    <t>e_won2</t>
+  </si>
+  <si>
+    <t>grid node -- won2</t>
+  </si>
+  <si>
+    <t>e_won20</t>
+  </si>
+  <si>
+    <t>grid node -- won20</t>
+  </si>
+  <si>
+    <t>e_won3</t>
+  </si>
+  <si>
+    <t>grid node -- won3</t>
+  </si>
+  <si>
+    <t>e_won4</t>
+  </si>
+  <si>
+    <t>grid node -- won4</t>
+  </si>
+  <si>
+    <t>e_won5</t>
+  </si>
+  <si>
+    <t>grid node -- won5</t>
+  </si>
+  <si>
+    <t>e_won6</t>
+  </si>
+  <si>
+    <t>grid node -- won6</t>
+  </si>
+  <si>
+    <t>e_won7</t>
+  </si>
+  <si>
+    <t>grid node -- won7</t>
+  </si>
+  <si>
+    <t>e_won8</t>
+  </si>
+  <si>
+    <t>grid node -- won8</t>
+  </si>
+  <si>
+    <t>e_won9</t>
+  </si>
+  <si>
+    <t>grid node -- won9</t>
   </si>
 </sst>
 </file>
@@ -5353,7 +5353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BBB0A9-71EA-4B64-A610-1E86851A7E05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA45059F-D0EE-4697-B919-2A9B1E42F144}">
   <dimension ref="B3:H64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CD7383-6A28-4B60-B33F-B72DF418A2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045A1B0F-88A7-45F5-A1A2-9864464818DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5353,7 +5353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA45059F-D0EE-4697-B919-2A9B1E42F144}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F49DB08-B15C-425F-A273-60C41F3C9C25}">
   <dimension ref="B3:H64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
